--- a/data/trans_orig/IP07A16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49759</t>
+          <t>49051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67880</t>
+          <t>67499</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51747</t>
+          <t>50549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69736</t>
+          <t>70297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107058</t>
+          <t>105997</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133243</t>
+          <t>132442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57335</t>
+          <t>57694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71980</t>
+          <t>72748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>98265</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123473</t>
+          <t>123850</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,48%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24807</t>
+          <t>25689</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>21996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25201</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42531</t>
+          <t>42823</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3512</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84777</t>
+          <t>85023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107660</t>
+          <t>106959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93603</t>
+          <t>93206</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115783</t>
+          <t>114654</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>185538</t>
+          <t>183140</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>215764</t>
+          <t>217076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66244</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88354</t>
+          <t>87677</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72867</t>
+          <t>72441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94682</t>
+          <t>95028</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145231</t>
+          <t>145092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176555</t>
+          <t>176228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>26074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44537</t>
+          <t>44093</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2906</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>141217</t>
+          <t>141130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>170193</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151318</t>
+          <t>150567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>180296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>298967</t>
+          <t>299590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>342634</t>
+          <t>341172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,4%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>111637</t>
+          <t>111218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>139724</t>
+          <t>139471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131597</t>
+          <t>129794</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159695</t>
+          <t>159506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248607</t>
+          <t>250093</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292369</t>
+          <t>292935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>27152</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>40815</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56279</t>
+          <t>56509</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80962</t>
+          <t>81764</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6411</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1182</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>5113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66450</t>
+          <t>66372</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87040</t>
+          <t>87411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>87847</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139478</t>
+          <t>139051</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168562</t>
+          <t>167662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57036</t>
+          <t>56595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77403</t>
+          <t>76428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49056</t>
+          <t>48435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68955</t>
+          <t>69984</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110851</t>
+          <t>111431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140459</t>
+          <t>140177</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13289</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12299</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25721</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35033</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3765</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5504</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>73864</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>94894</t>
+          <t>96134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87799</t>
+          <t>88066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>109221</t>
+          <t>109023</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3740,12 +3740,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167054</t>
+          <t>166774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197193</t>
+          <t>197602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -3803,12 +3803,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53367</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74046</t>
+          <t>74810</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52095</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72480</t>
+          <t>72667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112476</t>
+          <t>112504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141985</t>
+          <t>141806</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,6%</t>
         </is>
       </c>
     </row>
@@ -3916,12 +3916,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3951,12 +3951,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>16424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>31034</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4029,12 +4029,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>774</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4064,12 +4064,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4079,12 +4079,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11425</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>715</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145184</t>
+          <t>145896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>174149</t>
+          <t>175147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>161335</t>
+          <t>161566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190649</t>
+          <t>190103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>315991</t>
+          <t>314271</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>358765</t>
+          <t>359237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116830</t>
+          <t>117363</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146290</t>
+          <t>145733</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107595</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135649</t>
+          <t>135452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233344</t>
+          <t>233393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274072</t>
+          <t>274732</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -4598,12 +4598,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28708</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4613,12 +4613,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20542</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>37183</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39665</t>
+          <t>38062</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>60435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4711,12 +4711,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1686</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4726,12 +4726,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4746,12 +4746,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9171</t>
+          <t>8862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>1442</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2099</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10680</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de ayudarse entre los amigos en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102542</t>
+          <t>101779</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125143</t>
+          <t>124727</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>67,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95078</t>
+          <t>95145</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>117533</t>
+          <t>117238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>204218</t>
+          <t>203849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235162</t>
+          <t>234732</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -5397,12 +5397,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43618</t>
+          <t>43969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>63608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5412,12 +5412,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5432,12 +5432,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51005</t>
+          <t>50838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72067</t>
+          <t>71721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102318</t>
+          <t>101102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129240</t>
+          <t>130499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10012</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>24087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9806</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22099</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40235</t>
+          <t>40621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77591</t>
+          <t>76947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99243</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84777</t>
+          <t>84845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106705</t>
+          <t>106650</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169326</t>
+          <t>167909</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199916</t>
+          <t>199059</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51604</t>
+          <t>52886</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>72910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76621</t>
+          <t>77217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111850</t>
+          <t>113513</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141338</t>
+          <t>142687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>24049</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7091</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18075</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36234</t>
+          <t>37506</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -6305,12 +6305,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6345,7 +6345,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>217365</t>
+          <t>216261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>186005</t>
+          <t>185946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>218520</t>
+          <t>217062</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380451</t>
+          <t>382305</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424121</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>59,64%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100722</t>
+          <t>100133</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129039</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>111992</t>
+          <t>111627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142218</t>
+          <t>142207</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221450</t>
+          <t>220659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263300</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,88%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23663</t>
+          <t>23680</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41923</t>
+          <t>42420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18224</t>
+          <t>18563</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34803</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46788</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70583</t>
+          <t>72876</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6987,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>9888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15434</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7072,12 +7072,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5616</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7190,7 +7190,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A16-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07A16-Edad-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,2%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>60959</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>51358</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>70946</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>43,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,64%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>58591</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>49051</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>67499</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>49362</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>66786</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>46,4%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>38,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>60959</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>50549</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>70297</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105997</t>
+          <t>106748</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132442</t>
+          <t>132569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62257</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52606</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72323</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>44,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,53%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>51,6%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48452</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39371</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57694</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39780</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57278</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>45,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>62257</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>52851</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72748</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>44,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98265</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123850</t>
+          <t>122780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,08%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15820</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10179</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22870</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,32%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>17831</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12542</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>25689</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>12307</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24691</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,93%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>15820</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>10423</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21996</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,29%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25201</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42823</t>
+          <t>43686</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2920</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1387</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4434</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2474</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1174,107 +1174,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>647</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3594</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3238</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140171</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140171</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140171</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>126262</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>126262</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>126262</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140171</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140171</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140171</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>104369</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>93203</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>115572</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,67%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>95962</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>85023</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>106959</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>84990</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>106002</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>49,64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43,98%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>104369</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>93206</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>114654</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>51,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>183140</t>
+          <t>184068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217076</t>
+          <t>216518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>83149</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>72458</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>95122</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>35,51%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>77115</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65883</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>87677</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>67000</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>87032</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>39,89%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,08%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>83149</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>72441</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>95028</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>40,74%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145092</t>
+          <t>145915</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176228</t>
+          <t>177047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16554</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>11069</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24034</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,78%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>18378</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12297</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>25383</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12121</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25805</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,51%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,13%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16554</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10990</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23013</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44093</t>
+          <t>44904</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1743,92 +1743,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1217</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1217</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1856,107 +1856,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2906</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>3186</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>204072</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>285</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>193304</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>204072</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>165328</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>150600</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>179766</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>43,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>52,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>154553</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>141130</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>170443</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>141269</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>169210</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>165328</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>150567</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>180296</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>48,03%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299590</t>
+          <t>298752</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341172</t>
+          <t>340931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>145406</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>130878</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>159184</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>42,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>125567</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>111218</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>139471</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>111288</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>138973</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,29%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>34,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>145406</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>129794</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>159506</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>42,24%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>251704</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>292935</t>
+          <t>292512</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32374</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>24047</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>36209</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>27152</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>45400</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>27531</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>46387</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,33%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>32374</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>24018</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>40815</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>56541</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81764</t>
+          <t>82268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2443</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>2604</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>6035</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6251</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,81%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,21%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3123</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7208</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2543,102 +2543,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2605</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3788</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3527</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>3256</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>5113</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>344243</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>474</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>319566</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>319566</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>319566</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>344243</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2813,13 +2813,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2830,7 +2830,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2998,72 +2998,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77255</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67173</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>88457</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>49,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,87%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>77061</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>66372</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>87411</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>66573</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>87662</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>49,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>42,88%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56,47%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>77255</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>66993</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>88142</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139051</t>
+          <t>138955</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167662</t>
+          <t>168133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,98%</t>
         </is>
       </c>
     </row>
@@ -3111,72 +3111,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48025</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>68413</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,46%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>66960</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56595</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>76428</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56686</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>77159</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,26%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,37%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>58687</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48435</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69984</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>37,46%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111431</t>
+          <t>111712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140177</t>
+          <t>139948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,93%</t>
         </is>
       </c>
     </row>
@@ -3224,72 +3224,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18114</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12297</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25641</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8223</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13549</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4488</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>13991</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,31%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,75%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>18114</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>12299</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>25721</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,56%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19116</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35414</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -3337,107 +3337,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1193</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3758</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4155</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1927</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5519</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1168</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7015</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -3450,72 +3450,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1359</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4782</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4815</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4179</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5504</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -3563,57 +3563,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156674</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>154796</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>156674</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3680,72 +3680,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>98268</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>86726</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>109190</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>56,31%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>62,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>83924</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>73382</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>96134</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73675</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>94956</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>50,43%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44,1%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>98268</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88066</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>109023</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>56,31%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>166774</t>
+          <t>167833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197602</t>
+          <t>196767</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -3798,67 +3798,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>63112</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52520</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>74113</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,1%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,47%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>64277</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52288</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74810</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>53253</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>74642</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,63%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>63112</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53003</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72667</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112504</t>
+          <t>113315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141806</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -3906,72 +3906,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10134</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5645</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16473</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>5,81%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,44%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>12670</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8334</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>19503</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7686</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>7,61%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10134</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6112</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>16225</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3986,12 +3986,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>30870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4019,72 +4019,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6237</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3132</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>774</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7524</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7164</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6704</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4099,12 +4099,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4132,72 +4132,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3365</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2401</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6324</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3051</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>761</t>
+          <t>736</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -4245,57 +4245,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174500</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174500</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174500</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166404</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174500</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174500</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174500</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4362,72 +4362,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>175523</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>159073</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>189704</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>57,28%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>160985</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>145896</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>175147</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>146417</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>175495</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,12%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>54,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>175523</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>161566</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>190103</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>53,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314271</t>
+          <t>316580</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>359237</t>
+          <t>357149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>54,75%</t>
         </is>
       </c>
     </row>
@@ -4475,72 +4475,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>121799</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>107282</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>136526</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,78%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>32,39%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>131237</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>117363</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>145733</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>116690</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>144602</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>40,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>45,37%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>121799</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>107595</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>135452</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,78%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>233393</t>
+          <t>234619</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274732</t>
+          <t>274482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -4588,72 +4588,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>28247</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>20318</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>37017</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>20893</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>13996</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28683</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13702</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>28419</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,5%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>28247</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>20927</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>37183</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>39165</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60435</t>
+          <t>59960</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -4706,69 +4706,69 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>4306</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9314</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>4325</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1686</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9368</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>9386</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
         <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>4306</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8862</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -4781,12 +4781,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15202</t>
+          <t>14966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4814,72 +4814,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4285</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>3760</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8708</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>8448</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1298</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10721</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -4927,57 +4927,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>331174</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>321200</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>321200</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>321200</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>331174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5089,13 +5089,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de ayudarse entre los/as amigos/as, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5106,7 +5106,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5274,72 +5274,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>106534</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>95554</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>117450</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>57,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51,59%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>63,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>113275</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>101779</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>124727</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>102082</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>123981</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,17%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>106534</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>95145</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>117238</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>57,52%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,3%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203849</t>
+          <t>204163</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>234732</t>
+          <t>234673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,36%</t>
         </is>
       </c>
     </row>
@@ -5387,72 +5387,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61298</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52188</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72265</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>28,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,02%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>53731</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43969</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>63608</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43818</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>64286</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>29,02%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,74%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>34,35%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>61298</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50838</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71721</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>33,1%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5467,12 +5467,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101102</t>
+          <t>100979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>130499</t>
+          <t>129991</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -5500,72 +5500,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14640</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9007</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21374</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10012</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24087</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>10576</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>24293</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,59%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,01%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>14640</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>9505</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21061</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5580,12 +5580,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>40641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5613,72 +5613,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5488</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1547</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5366</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5422</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5731,102 +5731,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3996</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>724</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4112</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4238</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3964</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4767</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5386</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -5839,57 +5839,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>185217</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>185217</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>185217</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>185183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>185217</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>185217</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>185217</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5956,72 +5956,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>95959</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>84466</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>107534</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>55,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,53%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>61,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>87872</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76947</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97694</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>76417</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>98592</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>51,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>45,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>95959</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>84845</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>106650</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167909</t>
+          <t>166961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>199059</t>
+          <t>198982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,92%</t>
         </is>
       </c>
     </row>
@@ -6069,72 +6069,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65352</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54422</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>76662</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>44,05%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61778</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>52886</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72910</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>52106</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73954</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,44%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,2%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65352</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>55142</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>77217</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113513</t>
+          <t>111878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>142687</t>
+          <t>142723</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -6182,72 +6182,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>17030</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>16501</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>10723</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24049</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>10821</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>24262</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,73%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,33%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>11155</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>6421</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>17127</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19677</t>
+          <t>21005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -6295,72 +6295,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1582</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5562</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3364</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8698</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7913</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,59%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1582</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5228</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6390,12 +6390,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -6521,57 +6521,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169515</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169515</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169515</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6638,72 +6638,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>202492</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>186401</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>217787</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>56,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>51,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>201147</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>187710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>216261</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>186788</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>218359</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,71%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>202492</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>185946</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>217062</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>56,36%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>382305</t>
+          <t>380450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>425804</t>
+          <t>425342</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -6751,72 +6751,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126650</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111139</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141634</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,42%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>115509</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>100133</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>129206</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>100526</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>130922</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>32,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>36,43%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126650</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111627</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>142207</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>35,25%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>220659</t>
+          <t>219393</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263300</t>
+          <t>263587</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,92%</t>
         </is>
       </c>
     </row>
@@ -6864,72 +6864,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25795</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>18801</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>34869</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>32407</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23680</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>42420</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>24241</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>42601</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>9,14%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,68%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,96%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25795</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>18563</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>35150</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72876</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -6977,72 +6977,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3538</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>4911</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>1727</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>9888</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10411</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>3538</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8664</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -7095,102 +7095,102 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>724</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4305</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3571</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,2%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4535</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4667</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -7203,57 +7203,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>359264</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>354698</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>354698</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>354698</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>359264</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
